--- a/wishlist/wishlist-tracker.xlsx
+++ b/wishlist/wishlist-tracker.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SBX Dash for GEM — Wishlist Tracker</t>
+          <t>SpeedBX Dash for GEM — Wishlist Tracker</t>
         </is>
       </c>
     </row>
